--- a/Processed_Data/crops_out_check.xlsx
+++ b/Processed_Data/crops_out_check.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,46 +425,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Scenario_UKCEH</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Crop</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Avoided_prod_losses_weight</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ecosystem_type</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Exceeded</t>
         </is>
@@ -462,7 +474,7 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Base_v6b</t>
+          <t>Base_v7a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -471,7 +483,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3162109.014434628</v>
+        <v>3040111.026533533</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -487,14 +499,14 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>59.173976</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A1r/d/D/v6b</t>
+          <t>Health 50%, Bio 35%-v7a</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -503,7 +515,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3504615.106643267</v>
+        <v>3297838.734622715</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -519,14 +531,14 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>57.977925</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C1/d/D/v6b</t>
+          <t>Health 50%, Bio 40%-v7a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -535,7 +547,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3511600.672988965</v>
+        <v>3355111.558642534</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -551,14 +563,14 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>57.953531</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D1/d/D/v6b</t>
+          <t>Health 50%, Bio 45%-v7a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -567,7 +579,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3519315.895112674</v>
+        <v>3498293.61869208</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -583,14 +595,14 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>57.926589</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C2/d/D/v6b</t>
+          <t>Health 50%, Bio 50%-v7a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -599,7 +611,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4479651.57289468</v>
+        <v>3899127.315405533</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -615,14 +627,14 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>57.103581</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D2/d/D/v6b</t>
+          <t>Health 55%, Bio 40%-v7a</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -631,7 +643,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3860321.151740325</v>
+        <v>3383747.970652443</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -647,14 +659,14 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>57.633184</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D3/d/D/v6b</t>
+          <t>Health 55%, Bio 45%-v7a</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -663,7 +675,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4573931.699487402</v>
+        <v>3498293.61869208</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -679,14 +691,14 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>57.02296</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MTFR_v6b</t>
+          <t>Health 55%, Bio 50%-v7a</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -695,7 +707,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6358641.012429712</v>
+        <v>3899127.315405533</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -711,23 +723,23 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>55.496816</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Base_v6b</t>
+          <t>Health 60%, Bio 40%-v7a</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>790644.4210772475</v>
+        <v>3782184.922489639</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -743,23 +755,23 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>59.173976</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A1r/d/D/v6b</t>
+          <t>Health 60%, Bio 45%-v7a</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>895299.0603632205</v>
+        <v>4016069.708321427</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -775,23 +787,23 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>57.977925</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C1/d/D/v6b</t>
+          <t>Health 60%, Bio 50%-v7a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>897433.5389688504</v>
+        <v>4366896.887069101</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -807,23 +819,23 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>57.953531</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>D1/d/D/v6b</t>
+          <t>MTFR_v7a</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>899790.9679510948</v>
+        <v>6354917.566639272</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -839,14 +851,14 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>57.926589</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C2/d/D/v6b</t>
+          <t>Base_v7a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -855,7 +867,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1139912.89322367</v>
+        <v>753367.2581074686</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -871,14 +883,14 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>57.103581</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>D2/d/D/v6b</t>
+          <t>Health 50%, Bio 35%-v7a</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -887,7 +899,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>985080.2879350813</v>
+        <v>832117.3911347184</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -903,14 +915,14 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>57.633184</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>D3/d/D/v6b</t>
+          <t>Health 50%, Bio 40%-v7a</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -919,7 +931,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1163482.924871851</v>
+        <v>849617.4206963298</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -935,14 +947,14 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>57.02296</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MTFR_v6b</t>
+          <t>Health 50%, Bio 45%-v7a</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -951,7 +963,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1609660.253107428</v>
+        <v>893367.4946003576</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -967,7 +979,263 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>55.496816</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Health 50%, Bio 50%-v7a</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>994781.8288513833</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Semi_natural</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Health 55%, Bio 40%-v7a</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>858367.4354771356</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Semi_natural</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Health 55%, Bio 45%-v7a</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>893367.4946003576</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Semi_natural</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Health 55%, Bio 50%-v7a</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>994781.8288513833</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Semi_natural</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>57.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Health 60%, Bio 40%-v7a</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>965546.2306224098</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Semi_natural</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Health 60%, Bio 45%-v7a</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1024017.427080357</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Semi_natural</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Health 60%, Bio 50%-v7a</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1111724.221767275</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Semi_natural</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>57.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MTFR_v7a</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Potato</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1608729.391659818</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2040</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Semi_natural</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>55.5</v>
       </c>
     </row>
   </sheetData>
